--- a/pop_collection.xlsx
+++ b/pop_collection.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marita/Documents/GitHub/MFA2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2F4F2D-48E8-194F-B323-AC0E8FAAF417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66EA714E-C809-BE43-8C85-38BD97565B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{F5A2A48D-66FF-7245-BEF9-BCA50B34213A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="7">
   <si>
     <t>jan data</t>
   </si>
@@ -56,7 +56,7 @@
     <t>POPULATION</t>
   </si>
   <si>
-    <t>https://ec.europa.eu/eurostat/statistics-explained/index.php?title=Population_projections_in_the_EU</t>
+    <t>UN pred</t>
   </si>
 </sst>
 </file>
@@ -87,17 +87,18 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Helvetica Neue"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -145,13 +146,11 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color theme="1"/>
-      </right>
-      <top style="thin">
-        <color theme="1"/>
-      </top>
+      </left>
+      <right/>
+      <top/>
       <bottom/>
       <diagonal/>
     </border>
@@ -159,26 +158,140 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color theme="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <right style="thin">
+          <color theme="1"/>
+        </right>
+        <top style="thin">
+          <color theme="1"/>
+        </top>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -189,6 +302,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7E29B332-5E3D-0146-86C2-2E672AE44FF6}" name="Tabell1" displayName="Tabell1" ref="A1:C178" totalsRowShown="0" tableBorderDxfId="3">
+  <autoFilter ref="A1:C178" xr:uid="{7E29B332-5E3D-0146-86C2-2E672AE44FF6}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C178">
+    <sortCondition descending="1" ref="B1:B178"/>
+  </sortState>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{A362EF95-4277-1D4E-AD95-2128BCF783B4}" name="POPULATION" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{7D326672-17F5-C54B-B296-AF4F9315EDFB}" name="YEAR" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{4E2F251A-2927-564C-887E-71AE961E0BA6}" name="SOURCE" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -508,1158 +636,1976 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F7EE6BA-8051-384B-9022-BBBBAC730564}">
-  <dimension ref="A1:C104"/>
+  <dimension ref="A1:C178"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.33203125" customWidth="1"/>
-    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="2" max="2" width="13" style="6" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>45121000</v>
-      </c>
-      <c r="B2">
+      <c r="A2" s="1">
+        <v>33127478.499999996</v>
+      </c>
+      <c r="B2" s="5">
         <v>2100</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
+      <c r="A3" s="1">
+        <v>33302992</v>
+      </c>
+      <c r="B3" s="5">
+        <v>2099</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>33475731.5</v>
+      </c>
+      <c r="B4" s="5">
+        <v>2098</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>33645991.5</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2097</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>33811182.5</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2096</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>33974156.5</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2095</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>34136023</v>
+      </c>
+      <c r="B8" s="5">
+        <v>2094</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>34295239</v>
+      </c>
+      <c r="B9" s="5">
+        <v>2093</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>34453467</v>
+      </c>
+      <c r="B10" s="5">
+        <v>2092</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>34611809.5</v>
+      </c>
+      <c r="B11" s="5">
+        <v>2091</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>34774237</v>
+      </c>
+      <c r="B12" s="5">
+        <v>2090</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>34941503.5</v>
+      </c>
+      <c r="B13" s="5">
+        <v>2089</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>35109160.5</v>
+      </c>
+      <c r="B14" s="5">
+        <v>2088</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>35273592</v>
+      </c>
+      <c r="B15" s="5">
+        <v>2087</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>35436926</v>
+      </c>
+      <c r="B16" s="5">
+        <v>2086</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>35605149.5</v>
+      </c>
+      <c r="B17" s="5">
+        <v>2085</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>35778725.5</v>
+      </c>
+      <c r="B18" s="5">
+        <v>2084</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>35956990.5</v>
+      </c>
+      <c r="B19" s="5">
+        <v>2083</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>36139448.5</v>
+      </c>
+      <c r="B20" s="5">
+        <v>2082</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>36327926.5</v>
+      </c>
+      <c r="B21" s="5">
+        <v>2081</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>36524535</v>
+      </c>
+      <c r="B22" s="5">
+        <v>2080</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>36729337.5</v>
+      </c>
+      <c r="B23" s="5">
+        <v>2079</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>36942005</v>
+      </c>
+      <c r="B24" s="5">
+        <v>2078</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>37163397</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2077</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>37397887</v>
+      </c>
+      <c r="B26" s="5">
+        <v>2076</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>37644621.5</v>
+      </c>
+      <c r="B27" s="5">
+        <v>2075</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>37903808.5</v>
+      </c>
+      <c r="B28" s="5">
+        <v>2074</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>38173658</v>
+      </c>
+      <c r="B29" s="5">
+        <v>2073</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>38453573.5</v>
+      </c>
+      <c r="B30" s="5">
+        <v>2072</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>38741025</v>
+      </c>
+      <c r="B31" s="5">
+        <v>2071</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>39035769</v>
+      </c>
+      <c r="B32" s="5">
+        <v>2070</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>39337025</v>
+      </c>
+      <c r="B33" s="5">
+        <v>2069</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>39644110.5</v>
+      </c>
+      <c r="B34" s="5">
+        <v>2068</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>39956629</v>
+      </c>
+      <c r="B35" s="5">
+        <v>2067</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>40271850.5</v>
+      </c>
+      <c r="B36" s="5">
+        <v>2066</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>40590376</v>
+      </c>
+      <c r="B37" s="5">
+        <v>2065</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>40914110</v>
+      </c>
+      <c r="B38" s="5">
+        <v>2064</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>41240291.5</v>
+      </c>
+      <c r="B39" s="5">
+        <v>2063</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>41566222.5</v>
+      </c>
+      <c r="B40" s="5">
+        <v>2062</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>41892752.5</v>
+      </c>
+      <c r="B41" s="5">
+        <v>2061</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>42210838</v>
+      </c>
+      <c r="B42" s="5">
+        <v>2060</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>42521116.5</v>
+      </c>
+      <c r="B43" s="5">
+        <v>2059</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>42824437.5</v>
+      </c>
+      <c r="B44" s="5">
+        <v>2058</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>43121616.5</v>
+      </c>
+      <c r="B45" s="5">
+        <v>2057</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>43418722.5</v>
+      </c>
+      <c r="B46" s="5">
+        <v>2056</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>43702732.5</v>
+      </c>
+      <c r="B47" s="5">
+        <v>2055</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>43969185</v>
+      </c>
+      <c r="B48" s="5">
+        <v>2054</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>44229847.5</v>
+      </c>
+      <c r="B49" s="5">
+        <v>2053</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>44480747</v>
+      </c>
+      <c r="B50" s="5">
+        <v>2052</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>44712279.5</v>
+      </c>
+      <c r="B51" s="5">
+        <v>2051</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>44928557.5</v>
+      </c>
+      <c r="B52" s="5">
+        <v>2050</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>45140662</v>
+      </c>
+      <c r="B53" s="5">
+        <v>2049</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>45342101.5</v>
+      </c>
+      <c r="B54" s="5">
+        <v>2048</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>45529637.5</v>
+      </c>
+      <c r="B55" s="5">
+        <v>2047</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>45708980.5</v>
+      </c>
+      <c r="B56" s="5">
+        <v>2046</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>45879964</v>
+      </c>
+      <c r="B57" s="5">
+        <v>2045</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>46041010</v>
+      </c>
+      <c r="B58" s="5">
+        <v>2044</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>46187923</v>
+      </c>
+      <c r="B59" s="5">
+        <v>2043</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>46327609.5</v>
+      </c>
+      <c r="B60" s="5">
+        <v>2042</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>46463105</v>
+      </c>
+      <c r="B61" s="5">
+        <v>2041</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>46591674</v>
+      </c>
+      <c r="B62" s="5">
+        <v>2040</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>46714654.5</v>
+      </c>
+      <c r="B63" s="5">
+        <v>2039</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>46830185.5</v>
+      </c>
+      <c r="B64" s="5">
+        <v>2038</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>46940809</v>
+      </c>
+      <c r="B65" s="5">
+        <v>2037</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>47049469.5</v>
+      </c>
+      <c r="B66" s="5">
+        <v>2036</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>47154196</v>
+      </c>
+      <c r="B67" s="5">
+        <v>2035</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>47252139.5</v>
+      </c>
+      <c r="B68" s="5">
+        <v>2034</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>47344055.5</v>
+      </c>
+      <c r="B69" s="5">
+        <v>2033</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>47433522.5</v>
+      </c>
+      <c r="B70" s="5">
+        <v>2032</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>47523489</v>
+      </c>
+      <c r="B71" s="5">
+        <v>2031</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>47610519.5</v>
+      </c>
+      <c r="B72" s="5">
+        <v>2030</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>47685764.5</v>
+      </c>
+      <c r="B73" s="5">
+        <v>2029</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>47748566</v>
+      </c>
+      <c r="B74" s="5">
+        <v>2028</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>47802271</v>
+      </c>
+      <c r="B75" s="5">
+        <v>2027</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>47850792.5</v>
+      </c>
+      <c r="B76" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
         <v>49128297</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B77" s="5">
         <v>2025</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+      <c r="C77" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
         <v>48619695</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B78" s="5">
         <v>2024</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
+      <c r="C78" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
         <v>48085361</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B79" s="5">
         <v>2023</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+      <c r="C79" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
         <v>47486727</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B80" s="5">
         <v>2022</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
+      <c r="C80" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
         <v>47400798</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B81" s="5">
         <v>2021</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+      <c r="C81" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
         <v>47318050</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B82" s="5">
         <v>2020</v>
       </c>
-      <c r="C8" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
+      <c r="C82" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
         <v>46918951</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B83" s="5">
         <v>2019</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="C83" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
         <v>46645070</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B84" s="5">
         <v>2018</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+      <c r="C84" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
         <v>46497393</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B85" s="5">
         <v>2017</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="C85" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
         <v>46418884</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B86" s="5">
         <v>2016</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
+      <c r="C86" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
         <v>46425722</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B87" s="5">
         <v>2015</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="C87" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
         <v>46495744</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B88" s="5">
         <v>2014</v>
       </c>
-      <c r="C14" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+      <c r="C88" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
         <v>46712650</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B89" s="5">
         <v>2013</v>
       </c>
-      <c r="C15" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+      <c r="C89" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
         <v>46818216</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B90" s="5">
         <v>2012</v>
       </c>
-      <c r="C16" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
+      <c r="C90" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
         <v>46667175</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B91" s="5">
         <v>2011</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
+      <c r="C91" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
         <v>46486621</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B92" s="5">
         <v>2010</v>
       </c>
-      <c r="C18" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
+      <c r="C92" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
         <v>46239271</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B93" s="5">
         <v>2009</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
+      <c r="C93" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
         <v>45668938</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B94" s="5">
         <v>2008</v>
       </c>
-      <c r="C20" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
+      <c r="C94" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A95" s="2">
         <v>44784659</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B95" s="5">
         <v>2007</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
+      <c r="C95" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
         <v>44009969</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B96" s="5">
         <v>2006</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
+      <c r="C96" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
         <v>43296335</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B97" s="5">
         <v>2005</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
+      <c r="C97" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
         <v>42547454</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B98" s="5">
         <v>2004</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
+      <c r="C98" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" s="2">
         <v>41827836</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B99" s="5">
         <v>2003</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
+      <c r="C99" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
         <v>41035271</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B100" s="5">
         <v>2002</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
+      <c r="C100" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="2">
         <v>40665545</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B101" s="5">
         <v>2001</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
+      <c r="C101" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="2">
         <v>40470182</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B102" s="5">
         <v>2000</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
+      <c r="C102" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="2">
         <v>40303568</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B103" s="5">
         <v>1999</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
+      <c r="C103" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" s="2">
         <v>40143449</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B104" s="5">
         <v>1998</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
+      <c r="C104" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" s="2">
         <v>39971329</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B105" s="5">
         <v>1997</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
+      <c r="C105" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" s="2">
         <v>39808374</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B106" s="5">
         <v>1996</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
+      <c r="C106" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" s="2">
         <v>39639726</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B107" s="5">
         <v>1995</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
+      <c r="C107" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" s="2">
         <v>39458489</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B108" s="5">
         <v>1994</v>
       </c>
-      <c r="C34" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="4">
+      <c r="C108" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" s="2">
         <v>39264034</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B109" s="5">
         <v>1993</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
+      <c r="C109" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" s="2">
         <v>39051336</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B110" s="5">
         <v>1992</v>
       </c>
-      <c r="C36" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
+      <c r="C110" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" s="2">
         <v>38881416</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B111" s="5">
         <v>1991</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
+      <c r="C111" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" s="2">
         <v>38853227</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B112" s="5">
         <v>1990</v>
       </c>
-      <c r="C38" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
+      <c r="C112" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" s="2">
         <v>38802300</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B113" s="5">
         <v>1989</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
+      <c r="C113" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" s="2">
         <v>38731578</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B114" s="5">
         <v>1988</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
+      <c r="C114" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" s="2">
         <v>38638052</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B115" s="5">
         <v>1987</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
+      <c r="C115" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" s="2">
         <v>38531195</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B116" s="5">
         <v>1986</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
+      <c r="C116" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117" s="2">
         <v>38407829</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B117" s="5">
         <v>1985</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
+      <c r="C117" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" s="2">
         <v>38252899</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B118" s="5">
         <v>1984</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
+      <c r="C118" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119" s="2">
         <v>38090151</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B119" s="5">
         <v>1983</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
+      <c r="C119" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120" s="2">
         <v>37881873</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B120" s="5">
         <v>1982</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
+      <c r="C120" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121" s="2">
         <v>37635389</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B121" s="5">
         <v>1981</v>
       </c>
-      <c r="C47" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
+      <c r="C121" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122" s="2">
         <v>37346940</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B122" s="5">
         <v>1980</v>
       </c>
-      <c r="C48" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A49" s="4">
+      <c r="C122" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123" s="2">
         <v>37035719</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B123" s="5">
         <v>1979</v>
       </c>
-      <c r="C49" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A50" s="4">
+      <c r="C123" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124" s="2">
         <v>36694077</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B124" s="5">
         <v>1978</v>
       </c>
-      <c r="C50" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A51" s="4">
+      <c r="C124" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125" s="2">
         <v>36329199</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B125" s="5">
         <v>1977</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A52" s="4">
+      <c r="C125" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126" s="2">
         <v>35946425</v>
       </c>
-      <c r="B52" s="5">
+      <c r="B126" s="5">
         <v>1976</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A53" s="4">
+      <c r="C126" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A127" s="2">
         <v>35569375</v>
       </c>
-      <c r="B53" s="5">
+      <c r="B127" s="5">
         <v>1975</v>
       </c>
-      <c r="C53" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A54" s="4">
+      <c r="C127" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128" s="2">
         <v>35177294</v>
       </c>
-      <c r="B54" s="5">
+      <c r="B128" s="5">
         <v>1974</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A55" s="4">
+      <c r="C128" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A129" s="2">
         <v>34800600</v>
       </c>
-      <c r="B55" s="5">
+      <c r="B129" s="5">
         <v>1973</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A56" s="4">
+      <c r="C129" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A130" s="2">
         <v>34408338</v>
       </c>
-      <c r="B56" s="5">
+      <c r="B130" s="5">
         <v>1972</v>
       </c>
-      <c r="C56" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A57" s="4">
+      <c r="C130" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A131" s="2">
         <v>34040642</v>
       </c>
-      <c r="B57" s="5">
+      <c r="B131" s="5">
         <v>1971</v>
       </c>
-      <c r="C57" s="6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A58" s="7">
+      <c r="C131" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A132" s="3">
         <v>33980276</v>
       </c>
-      <c r="B58" s="5">
+      <c r="B132" s="5">
         <v>1970</v>
       </c>
-      <c r="C58" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A59" s="7">
+      <c r="C132" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A133" s="3">
         <v>33614193</v>
       </c>
-      <c r="B59" s="5">
+      <c r="B133" s="5">
         <v>1969</v>
       </c>
-      <c r="C59" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A60" s="7">
+      <c r="C133" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A134" s="3">
         <v>33265171</v>
       </c>
-      <c r="B60" s="5">
+      <c r="B134" s="5">
         <v>1968</v>
       </c>
-      <c r="C60" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A61" s="7">
+      <c r="C134" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A135" s="3">
         <v>32926306</v>
       </c>
-      <c r="B61" s="5">
+      <c r="B135" s="5">
         <v>1967</v>
       </c>
-      <c r="C61" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A62" s="7">
+      <c r="C135" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A136" s="3">
         <v>32587243</v>
       </c>
-      <c r="B62" s="5">
+      <c r="B136" s="5">
         <v>1966</v>
       </c>
-      <c r="C62" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A63" s="7">
+      <c r="C136" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A137" s="3">
         <v>32241041</v>
       </c>
-      <c r="B63" s="5">
+      <c r="B137" s="5">
         <v>1965</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A64" s="7">
+      <c r="C137" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A138" s="3">
         <v>31885404</v>
       </c>
-      <c r="B64" s="5">
+      <c r="B138" s="5">
         <v>1964</v>
       </c>
-      <c r="C64" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A65" s="7">
+      <c r="C138" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A139" s="3">
         <v>31524385</v>
       </c>
-      <c r="B65" s="5">
+      <c r="B139" s="5">
         <v>1963</v>
       </c>
-      <c r="C65" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A66" s="7">
+      <c r="C139" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A140" s="3">
         <v>31165074</v>
       </c>
-      <c r="B66" s="5">
+      <c r="B140" s="5">
         <v>1962</v>
       </c>
-      <c r="C66" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A67" s="7">
+      <c r="C140" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A141" s="3">
         <v>30817569</v>
       </c>
-      <c r="B67" s="5">
+      <c r="B141" s="5">
         <v>1961</v>
       </c>
-      <c r="C67" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="7">
+      <c r="C141" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A142" s="3">
         <v>30489241</v>
       </c>
-      <c r="B68" s="5">
+      <c r="B142" s="5">
         <v>1960</v>
       </c>
-      <c r="C68" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A69" s="7">
+      <c r="C142" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A143" s="3">
         <v>30182781</v>
       </c>
-      <c r="B69" s="5">
+      <c r="B143" s="5">
         <v>1959</v>
       </c>
-      <c r="C69" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A70" s="7">
+      <c r="C143" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A144" s="3">
         <v>29896928</v>
       </c>
-      <c r="B70" s="5">
+      <c r="B144" s="5">
         <v>1958</v>
       </c>
-      <c r="C70" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A71" s="7">
+      <c r="C144" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A145" s="3">
         <v>29628012</v>
       </c>
-      <c r="B71" s="5">
+      <c r="B145" s="5">
         <v>1957</v>
       </c>
-      <c r="C71" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A72" s="7">
+      <c r="C145" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A146" s="3">
         <v>29371820</v>
       </c>
-      <c r="B72" s="5">
+      <c r="B146" s="5">
         <v>1956</v>
       </c>
-      <c r="C72" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A73" s="7">
+      <c r="C146" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A147" s="3">
         <v>29125353</v>
       </c>
-      <c r="B73" s="5">
+      <c r="B147" s="5">
         <v>1955</v>
       </c>
-      <c r="C73" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A74" s="7">
+      <c r="C147" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A148" s="3">
         <v>28887349</v>
       </c>
-      <c r="B74" s="5">
+      <c r="B148" s="5">
         <v>1954</v>
       </c>
-      <c r="C74" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A75" s="7">
+      <c r="C148" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A149" s="3">
         <v>28658669</v>
       </c>
-      <c r="B75" s="5">
+      <c r="B149" s="5">
         <v>1953</v>
       </c>
-      <c r="C75" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A76" s="7">
+      <c r="C149" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A150" s="3">
         <v>28442373</v>
       </c>
-      <c r="B76" s="5">
+      <c r="B150" s="5">
         <v>1952</v>
       </c>
-      <c r="C76" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A77" s="7">
+      <c r="C150" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A151" s="3">
         <v>28243634</v>
       </c>
-      <c r="B77" s="5">
+      <c r="B151" s="5">
         <v>1951</v>
       </c>
-      <c r="C77" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A78" s="7">
+      <c r="C151" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A152" s="3">
         <v>28069735</v>
       </c>
-      <c r="B78" s="5">
+      <c r="B152" s="5">
         <v>1950</v>
       </c>
-      <c r="C78" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="9">
+      <c r="C152" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A153" s="4">
         <v>26014278</v>
       </c>
-      <c r="B79" s="5">
+      <c r="B153" s="5">
         <v>1940</v>
       </c>
-      <c r="C79" s="8" t="s">
+      <c r="C153" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="9">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A154" s="4">
         <v>23677095</v>
       </c>
-      <c r="B80" s="5">
+      <c r="B154" s="5">
         <v>1930</v>
       </c>
-      <c r="C80" s="8" t="s">
+      <c r="C154" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A81" s="9">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A155" s="4">
         <v>21388551</v>
       </c>
-      <c r="B81" s="5">
+      <c r="B155" s="5">
         <v>1920</v>
       </c>
-      <c r="C81" s="8" t="s">
+      <c r="C155" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A82" s="9">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A156" s="4">
         <v>19990669</v>
       </c>
-      <c r="B82" s="5">
+      <c r="B156" s="5">
         <v>1910</v>
       </c>
-      <c r="C82" s="8" t="s">
+      <c r="C156" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A83" s="9">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A157" s="4">
         <v>18616630</v>
       </c>
-      <c r="B83" s="5">
+      <c r="B157" s="5">
         <v>1900</v>
       </c>
-      <c r="C83" s="8" t="s">
+      <c r="C157" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A84" s="7">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A158" s="3">
         <v>18193230</v>
       </c>
-      <c r="B84" s="5">
+      <c r="B158" s="5">
         <v>1890</v>
       </c>
-      <c r="C84" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A85" s="7">
+      <c r="C158" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A159" s="3">
         <v>17388399</v>
       </c>
-      <c r="B85" s="5">
+      <c r="B159" s="5">
         <v>1880</v>
       </c>
-      <c r="C85" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A86" s="7">
+      <c r="C159" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A160" s="3">
         <v>16506588</v>
       </c>
-      <c r="B86" s="5">
+      <c r="B160" s="5">
         <v>1870</v>
       </c>
-      <c r="C86" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A87" s="7">
+      <c r="C160" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A161" s="3">
         <v>15666000</v>
       </c>
-      <c r="B87" s="5">
+      <c r="B161" s="5">
         <v>1860</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A88" s="7">
+      <c r="C161" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A162" s="3">
         <v>14215999</v>
       </c>
-      <c r="B88" s="5">
+      <c r="B162" s="5">
         <v>1850</v>
       </c>
-      <c r="C88" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A89" s="7">
+      <c r="C162" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A163" s="3">
         <v>13020117</v>
       </c>
-      <c r="B89" s="5">
+      <c r="B163" s="5">
         <v>1840</v>
       </c>
-      <c r="C89" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A90" s="7">
+      <c r="C163" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A164" s="3">
         <v>13040999</v>
       </c>
-      <c r="B90" s="5">
+      <c r="B164" s="5">
         <v>1830</v>
       </c>
-      <c r="C90" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A91" s="7">
+      <c r="C164" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A165" s="3">
         <v>12203000</v>
       </c>
-      <c r="B91" s="5">
+      <c r="B165" s="5">
         <v>1820</v>
       </c>
-      <c r="C91" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A92" s="7">
+      <c r="C165" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A166" s="3">
         <v>11873189</v>
       </c>
-      <c r="B92" s="5">
+      <c r="B166" s="5">
         <v>1810</v>
       </c>
-      <c r="C92" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A93" s="7">
+      <c r="C166" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A167" s="3">
         <v>11552292</v>
       </c>
-      <c r="B93" s="5">
+      <c r="B167" s="5">
         <v>1800</v>
       </c>
-      <c r="C93" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A94" s="7">
+      <c r="C167" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A168" s="3">
         <v>11240068</v>
       </c>
-      <c r="B94" s="5">
+      <c r="B168" s="5">
         <v>1790</v>
       </c>
-      <c r="C94" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A95" s="7">
+      <c r="C168" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A169" s="3">
         <v>10936282</v>
       </c>
-      <c r="B95" s="5">
+      <c r="B169" s="5">
         <v>1780</v>
       </c>
-      <c r="C95" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A96" s="7">
+      <c r="C169" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A170" s="3">
         <v>10640707</v>
       </c>
-      <c r="B96" s="5">
+      <c r="B170" s="5">
         <v>1770</v>
       </c>
-      <c r="C96" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A97" s="7">
+      <c r="C170" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A171" s="3">
         <v>10353120</v>
       </c>
-      <c r="B97" s="5">
+      <c r="B171" s="5">
         <v>1760</v>
       </c>
-      <c r="C97" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A98" s="7">
+      <c r="C171" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A172" s="3">
         <v>10073306</v>
       </c>
-      <c r="B98" s="5">
+      <c r="B172" s="5">
         <v>1750</v>
       </c>
-      <c r="C98" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A99" s="7">
+      <c r="C172" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A173" s="3">
         <v>9801054</v>
       </c>
-      <c r="B99" s="5">
+      <c r="B173" s="5">
         <v>1740</v>
       </c>
-      <c r="C99" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A100" s="7">
+      <c r="C173" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A174" s="3">
         <v>9536161</v>
       </c>
-      <c r="B100" s="5">
+      <c r="B174" s="5">
         <v>1730</v>
       </c>
-      <c r="C100" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A101" s="7">
+      <c r="C174" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A175" s="3">
         <v>9278427</v>
       </c>
-      <c r="B101" s="5">
+      <c r="B175" s="5">
         <v>1720</v>
       </c>
-      <c r="C101" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A102" s="7">
+      <c r="C175" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A176" s="3">
         <v>9027659</v>
       </c>
-      <c r="B102" s="5">
+      <c r="B176" s="5">
         <v>1710</v>
       </c>
-      <c r="C102" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A103" s="7">
+      <c r="C176" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A177" s="3">
         <v>8000000</v>
       </c>
-      <c r="B103" s="5">
+      <c r="B177" s="5">
         <v>1700</v>
       </c>
-      <c r="C103" s="8" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A104" s="7">
+      <c r="C177" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A178" s="3">
         <v>8500000</v>
       </c>
-      <c r="B104" s="5">
+      <c r="B178" s="5">
         <v>1600</v>
       </c>
-      <c r="C104" s="8" t="s">
+      <c r="C178" s="3" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>